--- a/backend/templates/发货录入样表.xlsx
+++ b/backend/templates/发货录入样表.xlsx
@@ -508,12 +508,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J-PETWOODSTAIRS-HUI-2PCS-FBA</t>
+          <t>DEMO-SKU-001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>X0054S6R65</t>
+          <t>X0DEMO0001</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -544,12 +544,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J-PETWOODSTAIRS-HUI-3PCS-FBA</t>
+          <t>DEMO-SKU-002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>X0054SLKIZ</t>
+          <t>X0DEMO0002</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -578,12 +578,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J-PETWOODSTAIRS-HUI-4PCS-FBA</t>
+          <t>DEMO-SKU-003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>X0054S6RG5</t>
+          <t>X0DEMO0003</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -612,12 +612,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J-PETWOODSTAIRS-ZHONG-2PCS-FBA</t>
+          <t>DEMO-SKU-004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>X0054SPAGN</t>
+          <t>X0DEMO0004</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -646,12 +646,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J-PETWOODSTAIRS-ZHONG-3PCS-FBA</t>
+          <t>DEMO-SKU-005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>X0054SLLEX</t>
+          <t>X0DEMO0005</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -680,12 +680,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J-PETWOODSTAIRS-ZHONG-4PCS-FBA</t>
+          <t>DEMO-SKU-006</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>X0054SLLFH</t>
+          <t>X0DEMO0006</t>
         </is>
       </c>
       <c r="C8" t="n">
